--- a/generator/diplo/sample_data_kaznu.xlsx
+++ b/generator/diplo/sample_data_kaznu.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ediploma\generator\diplo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73638E69-8A8D-40FB-B4A9-37F47E95B084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF85710-D07F-4B29-A34B-4CD9B4DA0015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="докторантура" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">докторантура!$A$3:$Z$10</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -462,26 +459,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -768,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B845E5-CF83-46D4-89D3-7E7F700D2418}">
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="5"/>
@@ -796,13 +793,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
@@ -828,32 +825,32 @@
       </c>
       <c r="Q1" s="17"/>
       <c r="R1" s="18"/>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="14" t="s">
+      <c r="V1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="14" t="s">
+      <c r="W1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Y1" s="14" t="s">
+      <c r="Y1" s="19" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
       <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
@@ -893,70 +890,106 @@
       <c r="R2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="J3" s="4"/>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="M3" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="O3" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="7"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
+      <c r="S3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="2">
+        <v>3.77</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="W3" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="X3" s="12">
+        <v>87778564949</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="4" spans="1:25" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="H4" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="3" t="s">
@@ -977,51 +1010,51 @@
         <v>34</v>
       </c>
       <c r="T4" s="2">
-        <v>3.77</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>50</v>
+        <v>3.63</v>
+      </c>
+      <c r="U4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="W4" s="13" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="X4" s="12">
-        <v>87778564949</v>
+        <v>87018883617</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="3" t="s">
@@ -1042,51 +1075,51 @@
         <v>34</v>
       </c>
       <c r="T5" s="2">
-        <v>3.63</v>
-      </c>
-      <c r="U5" s="10" t="s">
-        <v>27</v>
+        <v>3.7</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="W5" s="13" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="X5" s="12">
-        <v>87018883617</v>
-      </c>
-      <c r="Y5" s="3" t="s">
-        <v>53</v>
+        <v>87772514040</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="3" t="s">
@@ -1107,51 +1140,51 @@
         <v>34</v>
       </c>
       <c r="T6" s="2">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="W6" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="X6" s="12">
-        <v>87772514040</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>68</v>
+        <v>87029375657</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="3" t="s">
@@ -1172,51 +1205,51 @@
         <v>34</v>
       </c>
       <c r="T7" s="2">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="W7" s="13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="X7" s="12">
-        <v>87029375657</v>
+        <v>87055252525</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="3" t="s">
@@ -1237,51 +1270,51 @@
         <v>34</v>
       </c>
       <c r="T8" s="2">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="W8" s="13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="X8" s="12">
-        <v>87055252525</v>
+        <v>87476277777</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="3" t="s">
@@ -1302,102 +1335,26 @@
         <v>34</v>
       </c>
       <c r="T9" s="2">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="W9" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X9" s="12">
-        <v>87476277777</v>
+        <v>87075748232</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="140.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="T10" s="2">
-        <v>3.93</v>
-      </c>
-      <c r="U10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="W10" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="X10" s="12">
-        <v>87075748232</v>
-      </c>
-      <c r="Y10" s="3" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Z10" xr:uid="{F0B845E5-CF83-46D4-89D3-7E7F700D2418}"/>
   <mergeCells count="17">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
     <mergeCell ref="X1:X2"/>
     <mergeCell ref="Y1:Y2"/>
     <mergeCell ref="S1:S2"/>
@@ -1405,15 +1362,25 @@
     <mergeCell ref="U1:U2"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="W1:W2"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="W4" r:id="rId1" xr:uid="{72F65B7B-CC82-48B8-BBE5-661BADA831E8}"/>
-    <hyperlink ref="W7" r:id="rId2" xr:uid="{A0FEA329-1C51-433C-9EB7-54FE05E2F6F2}"/>
-    <hyperlink ref="W8" r:id="rId3" xr:uid="{9DE52E0B-CF9C-4153-9E64-F9B7CFD8D275}"/>
-    <hyperlink ref="W6" r:id="rId4" xr:uid="{7DE98F55-8228-4877-8CCF-5EFAD327F27E}"/>
-    <hyperlink ref="W10" r:id="rId5" xr:uid="{5DF61EFC-DA32-4C16-82F7-C110A0BB73F8}"/>
-    <hyperlink ref="W9" r:id="rId6" xr:uid="{6CF9F2CC-BD19-4847-A1E8-8F28F826B27D}"/>
-    <hyperlink ref="W5" r:id="rId7" xr:uid="{936CFBDF-CA27-403F-801D-08F53B3F47E8}"/>
+    <hyperlink ref="W3" r:id="rId1" xr:uid="{72F65B7B-CC82-48B8-BBE5-661BADA831E8}"/>
+    <hyperlink ref="W6" r:id="rId2" xr:uid="{A0FEA329-1C51-433C-9EB7-54FE05E2F6F2}"/>
+    <hyperlink ref="W7" r:id="rId3" xr:uid="{9DE52E0B-CF9C-4153-9E64-F9B7CFD8D275}"/>
+    <hyperlink ref="W5" r:id="rId4" xr:uid="{7DE98F55-8228-4877-8CCF-5EFAD327F27E}"/>
+    <hyperlink ref="W9" r:id="rId5" xr:uid="{5DF61EFC-DA32-4C16-82F7-C110A0BB73F8}"/>
+    <hyperlink ref="W8" r:id="rId6" xr:uid="{6CF9F2CC-BD19-4847-A1E8-8F28F826B27D}"/>
+    <hyperlink ref="W4" r:id="rId7" xr:uid="{936CFBDF-CA27-403F-801D-08F53B3F47E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>

--- a/generator/diplo/sample_data_kaznu.xlsx
+++ b/generator/diplo/sample_data_kaznu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ediploma\generator\diplo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF85710-D07F-4B29-A34B-4CD9B4DA0015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866E1249-CFA8-4A29-8C46-12D71EE69B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -459,26 +459,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -769,37 +769,39 @@
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="5"/>
-    <col min="2" max="2" width="55.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" style="5" customWidth="1"/>
-    <col min="4" max="6" width="47.6640625" style="5" customWidth="1"/>
-    <col min="7" max="8" width="36.5546875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="39.6640625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="37" style="5" customWidth="1"/>
-    <col min="11" max="11" width="67" style="5" customWidth="1"/>
-    <col min="12" max="12" width="24.44140625" style="5" customWidth="1"/>
-    <col min="13" max="13" width="68.6640625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="24.44140625" style="5" customWidth="1"/>
-    <col min="15" max="15" width="96.44140625" style="5" customWidth="1"/>
-    <col min="16" max="18" width="24.44140625" style="5" customWidth="1"/>
-    <col min="19" max="19" width="21.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="12.44140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="21.21875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="18.44140625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="19.88671875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="25.109375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="25.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="5" customWidth="1"/>
+    <col min="4" max="5" width="38.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="15.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="39" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" style="5" customWidth="1"/>
+    <col min="13" max="13" width="44.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="39.44140625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="9.5546875" style="5" customWidth="1"/>
+    <col min="17" max="17" width="7.44140625" style="5" customWidth="1"/>
+    <col min="18" max="18" width="7.33203125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="50.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="28.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="12.109375" style="1" customWidth="1"/>
     <col min="27" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="16" t="s">
@@ -825,32 +827,32 @@
       </c>
       <c r="Q1" s="17"/>
       <c r="R1" s="18"/>
-      <c r="S1" s="19" t="s">
+      <c r="S1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="T1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="U1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="19" t="s">
+      <c r="V1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="19" t="s">
+      <c r="W1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="X1" s="19" t="s">
+      <c r="X1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="Y1" s="19" t="s">
+      <c r="Y1" s="14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
       <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
@@ -890,13 +892,13 @@
       <c r="R2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
     </row>
     <row r="3" spans="1:25" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
@@ -1355,6 +1357,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:O1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
     <mergeCell ref="X1:X2"/>
     <mergeCell ref="Y1:Y2"/>
     <mergeCell ref="S1:S2"/>
@@ -1362,16 +1374,6 @@
     <mergeCell ref="U1:U2"/>
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="W1:W2"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="P1:R1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="W3" r:id="rId1" xr:uid="{72F65B7B-CC82-48B8-BBE5-661BADA831E8}"/>
